--- a/MavenBook/src/test/resources/PaymentData.xlsx
+++ b/MavenBook/src/test/resources/PaymentData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Customer Name</t>
   </si>
@@ -43,19 +43,37 @@
     <t>Test</t>
   </si>
   <si>
-    <t>Subin</t>
-  </si>
-  <si>
-    <t>PI47</t>
-  </si>
-  <si>
     <t>1000</t>
   </si>
   <si>
     <t>Cash</t>
   </si>
   <si>
-    <t>16426-01</t>
+    <t>500</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>160726-1</t>
+  </si>
+  <si>
+    <t>160726-2</t>
+  </si>
+  <si>
+    <t>160726-3</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>PI488</t>
+  </si>
+  <si>
+    <t>PI484</t>
+  </si>
+  <si>
+    <t>PI481</t>
   </si>
 </sst>
 </file>
@@ -112,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,6 +152,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="2" customWidth="1"/>
@@ -483,22 +504,22 @@
       <c r="K1" s="9"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>8</v>
@@ -507,21 +528,58 @@
       <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="I3" s="6"/>
       <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C4:C12" numberStoredAsText="1"/>
+    <ignoredError sqref="C5:C8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>